--- a/www/download/IND.surplus_value.empe.r.pc.EXI382.xlsx
+++ b/www/download/IND.surplus_value.empe.r.pc.EXI382.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,144 +688,144 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>0.326170304643834</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>-0.00162486259661354</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-0.160381475452005</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>-0.00909193590124657</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-24.89</t>
+          <t>-0.307543815826258</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-0.135756739037145</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.104940093130389</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.0904315328205323</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.082941147147905</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-24.67</t>
+          <t>-0.301063957988933</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-21.47</t>
+          <t>-0.268536085949019</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-19.25</t>
+          <t>-0.245976622945119</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-0.0709012337160024</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-5.23</t>
+          <t>-0.109922123713151</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-0.102714728346944</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>-11.99</t>
+          <t>-0.173234880355795</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-12.88</t>
+          <t>-0.18579644774559</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-0.150329056888365</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>-12.99</t>
+          <t>-0.1813848813089</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>0.112570003852088</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>0.272990922842639</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0132068614941929</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>0.0303338853243189</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>0.075943499184062</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>15.95</t>
+          <t>0.0949801089242677</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>0.0137251687855806</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>0.0362786488657223</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -830,144 +835,144 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>0.129733780839015</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-6.8</t>
+          <t>-0.214438400910031</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-22.51</t>
+          <t>-0.34072963034264</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>0.0273917990283663</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-0.278055163535807</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>-0.0791768748056187</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>-0.0263318278462337</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>0.0495654984853187</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>0.0877777312031252</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>25.44</t>
+          <t>0.0633071411696511</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>0.14859208468568</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>0.123822269363254</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>55.08</t>
+          <t>0.3113437379317</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>43.29</t>
+          <t>0.212356091750763</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>0.15745483807714</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>0.0904824916047213</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>0.0803002633900842</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>37.29</t>
+          <t>0.145839155666015</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>36.74</t>
+          <t>0.139125236480751</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>0.213945531594634</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>0.253340283714377</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>0.00651998099293594</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>0.0828631420682726</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>-0.0332057462535601</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>0.10790187857069</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>-0.00793914846655197</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>0.201969746598689</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -977,144 +982,144 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-56.72</t>
+          <t>-0.637698070138751</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-48.59</t>
+          <t>-0.573414190318023</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-63.21</t>
+          <t>-0.688762980430717</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-52.44</t>
+          <t>-0.597951070051325</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-60.07</t>
+          <t>-0.668174776495778</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-59.4</t>
+          <t>-0.65955436975891</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-44.61</t>
+          <t>-0.534363105511285</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-44.7</t>
+          <t>-0.532535399284622</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-44.03</t>
+          <t>-0.520509720172988</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.81</t>
+          <t>-0.579831597403598</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-54.72</t>
+          <t>-0.610948349773882</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-56.37</t>
+          <t>-0.626790924971104</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-51.41</t>
+          <t>-0.575738852350177</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-44.84</t>
+          <t>-0.523474604350353</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-48.46</t>
+          <t>-0.55809598833397</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>-45.56</t>
+          <t>-0.535250179487667</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-35.96</t>
+          <t>-0.455181748133467</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>-48.7</t>
+          <t>-0.568482015207628</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>-42.34</t>
+          <t>-0.513210716238211</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-34.44</t>
+          <t>-0.441771202368013</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-38.23</t>
+          <t>-0.483065023386283</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>-48.04</t>
+          <t>-0.561887006715459</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>-44.85</t>
+          <t>-0.529121844576704</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>-51.63</t>
+          <t>-0.589746897556414</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-41.96</t>
+          <t>-0.504305115137311</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-50.17</t>
+          <t>-0.578647578603998</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>-49.79</t>
+          <t>-0.578962577309486</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1124,144 +1129,144 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>652.63</t>
+          <t>5.79127152825271</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>383.64</t>
+          <t>3.34088122582201</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>310.41</t>
+          <t>2.74413373581596</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>341.34</t>
+          <t>3.00277353776523</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>316.76</t>
+          <t>2.75188947874185</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>308.22</t>
+          <t>2.70432374987994</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>393.92</t>
+          <t>3.41493766554986</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>418.62</t>
+          <t>3.7241824983602</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>429.75</t>
+          <t>3.8004925634671</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>408.57</t>
+          <t>3.58544599960957</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>420.12</t>
+          <t>3.73722737319327</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>351.66</t>
+          <t>3.12819875388243</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>426.44</t>
+          <t>3.7831268798066</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>370.52</t>
+          <t>3.2228473632497</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>297.04</t>
+          <t>2.57978431693872</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>311.49</t>
+          <t>2.67346602287086</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>303.81</t>
+          <t>2.56683696096444</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>321.37</t>
+          <t>2.74059934552863</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>292.85</t>
+          <t>2.47445976786904</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>292.19</t>
+          <t>2.43087939596005</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>283.68</t>
+          <t>2.36566078345649</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>271.72</t>
+          <t>2.26441683862562</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>360.8</t>
+          <t>3.02922464942478</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>236.43</t>
+          <t>1.97151749692834</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>250.86</t>
+          <t>2.11528509503771</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>219.8</t>
+          <t>1.83514362594031</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>424.89</t>
+          <t>3.63870115304961</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1271,144 +1276,144 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>170.69</t>
+          <t>1.65041833130665</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-50.81</t>
+          <t>-0.510391667850247</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-32.05</t>
+          <t>-0.326863051480877</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-42.17</t>
+          <t>-0.428818512626584</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-38.94</t>
+          <t>-0.396410861184682</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-44.59</t>
+          <t>-0.45355756380624</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-29.29</t>
+          <t>-0.300740658628581</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-10.86</t>
+          <t>-0.120471081708748</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-0.0687298726513198</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-0.0648583070152317</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-0.0302647447940916</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-6.68</t>
+          <t>-0.0779290889802219</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>0.0594011066421187</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>0.0834371879508906</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>0.182964876954886</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>0.192492533084735</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>0.275719276420331</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>41.44</t>
+          <t>0.376693142009484</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>0.391084712823925</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>194.26</t>
+          <t>1.88755295900381</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>220.98</t>
+          <t>2.15632718038374</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>201.29</t>
+          <t>1.95228453364126</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>179.9</t>
+          <t>1.73858771339818</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>202.23</t>
+          <t>1.95350856568619</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>208.29</t>
+          <t>2.01725005166235</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>197.67</t>
+          <t>1.90305178298881</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>170.82</t>
+          <t>1.63095911920604</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1418,144 +1423,144 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-79.67</t>
+          <t>-0.793393843842962</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>54.59</t>
+          <t>0.431325640686062</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>71.59</t>
+          <t>0.582483426981921</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>67.32</t>
+          <t>0.541876509576505</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>53.92</t>
+          <t>0.406861083080154</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>64.78</t>
+          <t>0.52262283090088</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>62.21</t>
+          <t>0.491633492002229</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>0.48480883691388</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>0.507217706246726</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>59.41</t>
+          <t>0.485830264356236</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>0.488678631713657</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>0.442106218766317</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>68.59</t>
+          <t>0.598672372824419</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>64.59</t>
+          <t>0.540259865112379</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>69.03</t>
+          <t>0.574430283009295</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>0.427880168714479</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>0.418724240282774</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>0.346882827211984</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>0.451749995090324</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>70.12</t>
+          <t>0.571750421786533</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>62.54</t>
+          <t>0.500245709318491</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>0.357771272440317</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>0.317382897159499</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>38.37</t>
+          <t>0.29077628914767</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>33.99</t>
+          <t>0.252447561685155</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>0.213493754536109</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>0.268037235716906</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1565,144 +1570,144 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>67.62</t>
+          <t>0.730097444860332</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-326.13</t>
+          <t>-3.34449663233228</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-226.19</t>
+          <t>-2.29534743604659</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-180.28</t>
+          <t>-1.81770211219485</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-229.92</t>
+          <t>-2.32914728843925</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-225.68</t>
+          <t>-2.28091930625369</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-219.22</t>
+          <t>-2.21521521435837</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-207</t>
+          <t>-2.09525764050083</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-209.7</t>
+          <t>-2.12750749123171</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-248.77</t>
+          <t>-2.53582143781362</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-259.82</t>
+          <t>-2.65439036350253</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>-218.89</t>
+          <t>-2.23371995829924</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>-224.5</t>
+          <t>-2.30218031260992</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>-221.63</t>
+          <t>-2.2640881292031</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-212.5</t>
+          <t>-2.16998233347902</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>-217.83</t>
+          <t>-2.22752317230352</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>-210.3</t>
+          <t>-2.14792802981987</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>-213.23</t>
+          <t>-2.16866908257248</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>-218.29</t>
+          <t>-2.22680668341615</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>-28.65</t>
+          <t>-0.267884518248796</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-17.36</t>
+          <t>-0.149400196203255</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>-31.88</t>
+          <t>-0.286182943291607</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>-14.23</t>
+          <t>-0.123180100153894</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>-31.12</t>
+          <t>-0.280713373363038</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>0.089508208477701</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-23.28</t>
+          <t>-0.196943178980543</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>-22.89</t>
+          <t>-0.192750189265619</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1712,144 +1717,144 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>0.491908053879914</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-47.76</t>
+          <t>-0.519300461548118</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-33.9</t>
+          <t>-0.386397562357011</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-44.24</t>
+          <t>-0.482711354783898</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-45.34</t>
+          <t>-0.500687265617639</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-50.42</t>
+          <t>-0.550501451815706</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-0.161966007054882</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>-0.0417132651561739</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-0.0788809209779975</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>0.0666170547835765</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>0.128939551521235</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>77.14</t>
+          <t>0.599705492999694</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>106.34</t>
+          <t>0.879233812342148</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>112.51</t>
+          <t>0.920786613273385</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>58.98</t>
+          <t>0.437516219753229</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>97.23</t>
+          <t>0.746023084671722</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>182.09</t>
+          <t>1.51907572953004</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>159.43</t>
+          <t>1.27158906161307</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>158.32</t>
+          <t>1.24812562801563</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>190.02</t>
+          <t>1.54021204759548</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>161.34</t>
+          <t>1.31032637211977</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>148.86</t>
+          <t>1.18989978266547</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>189.09</t>
+          <t>1.579694684438</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>203.62</t>
+          <t>1.65396982423446</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>192.17</t>
+          <t>1.58331271110176</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>1.66470059508697</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>569.32</t>
+          <t>5.29883456804677</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1859,144 +1864,144 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>176.79</t>
+          <t>1.43576726248856</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>171.78</t>
+          <t>1.38112709933139</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>123.04</t>
+          <t>0.979860513529847</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>178.17</t>
+          <t>1.45377665759577</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>148.45</t>
+          <t>1.20710213870216</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>165.69</t>
+          <t>1.35834980018233</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>213.97</t>
+          <t>1.78585002777158</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>146.94</t>
+          <t>1.14179554533279</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>212.72</t>
+          <t>1.73143794465768</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>156.42</t>
+          <t>1.27023624815764</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>137.4</t>
+          <t>1.09291276430646</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>0.904939774301242</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>129.15</t>
+          <t>1.01814396664307</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>146.02</t>
+          <t>1.14293569735833</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>174.22</t>
+          <t>1.44498339053395</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>152.11</t>
+          <t>1.21779617834133</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>184.73</t>
+          <t>1.49129605548828</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>152.92</t>
+          <t>1.22255293024322</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>170.6</t>
+          <t>1.37342886584656</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>158.11</t>
+          <t>1.29236758248734</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>113.23</t>
+          <t>0.899976032993014</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>111.86</t>
+          <t>0.892278038208293</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>147.24</t>
+          <t>1.23296204064317</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>138.87</t>
+          <t>1.14198091639837</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>116.83</t>
+          <t>0.953290796297291</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>109.37</t>
+          <t>0.883932416753558</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>119.28</t>
+          <t>0.958052160367661</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2006,144 +2011,144 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>0.00248784564534521</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-15.82</t>
+          <t>-0.239525952066432</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-12.65</t>
+          <t>-0.199374725165228</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-12.9</t>
+          <t>-0.206777837385267</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-13.8</t>
+          <t>-0.219609711862238</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-0.224176185284961</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>16.77</t>
+          <t>0.0612663288922719</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-0.108322780578426</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-8.22</t>
+          <t>-0.151891577149474</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-0.023615660909698</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>0.00673194326541093</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.0927571205465965</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>0.119426133123866</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>0.0675746707914178</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>0.104357349011076</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>0.0353108890878457</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>20.61</t>
+          <t>0.111472808613565</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>0.144541681680272</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>20.94</t>
+          <t>0.108283627536307</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>0.101019552301999</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>41.56</t>
+          <t>0.324523477450642</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>0.188784765022938</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>0.143027856397897</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>0.1835871302445</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>29.86</t>
+          <t>0.220654761196289</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>0.0382862554247423</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>0.123293688319837</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2153,144 +2158,144 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>0.0259283506171146</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>38.39</t>
+          <t>0.208650804715549</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>44.64</t>
+          <t>0.300261727119119</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>0.394736710905225</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>0.112738308507907</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>0.121063756223605</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>0.0775697614891324</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>18.29</t>
+          <t>0.0807211057784072</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>0.0906813695982631</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>0.137288540694706</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>16.27</t>
+          <t>0.0734920747364585</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>17.28</t>
+          <t>0.0809267660250803</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>44.34</t>
+          <t>0.338493899109025</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>0.214724127633531</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>35.93</t>
+          <t>0.224760689881261</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>0.307434698505566</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>0.171655206122402</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>0.262370814175254</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>0.0666512952810134</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>0.256927925461641</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>49.08</t>
+          <t>0.38540817944231</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>0.280357276038921</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>0.329831511868251</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>0.171492039620943</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>0.371137484895559</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>0.151258852608663</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>26.83</t>
+          <t>0.164281632393802</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2300,144 +2305,144 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-0.134389052188936</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>0.681977615169554</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>87.95</t>
+          <t>0.694452435458917</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>79.49</t>
+          <t>0.611806743055159</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>74.41</t>
+          <t>0.555796458979479</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>78.72</t>
+          <t>0.594465333118474</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>70.97</t>
+          <t>0.526899302068776</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>0.511083416909023</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>90.07</t>
+          <t>0.723660166948995</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>75.63</t>
+          <t>0.586452176200736</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>72.53</t>
+          <t>0.562550946885391</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>86.16</t>
+          <t>0.675844723386752</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>102.38</t>
+          <t>0.855785665670259</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>0.713094865406691</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>122.56</t>
+          <t>1.03697194914237</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>115.78</t>
+          <t>0.97654875949421</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>0.952739519369092</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>111.14</t>
+          <t>0.919008115878249</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>101.42</t>
+          <t>0.819530172746379</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>112.22</t>
+          <t>0.973902168018022</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>117.2</t>
+          <t>1.0266656899055</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>105.71</t>
+          <t>0.939835012797519</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>80.88</t>
+          <t>0.741691234229747</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>0.384096052904784</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>0.597683746365345</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>0.475754934274652</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>48.63</t>
+          <t>0.419460439164896</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2447,144 +2452,144 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>212.54</t>
+          <t>1.73047192847357</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>40.97</t>
+          <t>0.258646876157911</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>0.233748256311767</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>0.286392683542675</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>51.77</t>
+          <t>0.426540145617837</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>0.271315020676707</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>0.552867472181633</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>0.230168531233889</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>27.45</t>
+          <t>0.19957581509181</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>118.13</t>
+          <t>0.952754862003249</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>91.01</t>
+          <t>0.707913870488453</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>0.107471441955188</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>60.82</t>
+          <t>0.492966170832957</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>0.155483490386536</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>0.173338975123145</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>-0.0205690839661498</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>49.58</t>
+          <t>0.390574015710965</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>0.0161951259071955</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>0.153032549888572</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>0.512221981308601</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>93.91</t>
+          <t>0.838488479504039</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>0.353707440188743</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>57.61</t>
+          <t>0.527341854458176</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>0.439095582735475</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>78.47</t>
+          <t>0.719256531837487</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>55.79</t>
+          <t>0.495636784369546</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>138.88</t>
+          <t>1.2289406140943</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2594,144 +2599,144 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>-0.0132709412842168</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-0.0863950202007814</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-0.0997001504690973</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-0.0164932453376759</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>0.046622907670802</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>0.0532833002846949</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>0.0592607319238276</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>21.42</t>
+          <t>0.159362210355407</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>22.76</t>
+          <t>0.176158561720178</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>24.06</t>
+          <t>0.159879792529268</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>0.111846521427721</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>0.165771619028434</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>65.85</t>
+          <t>0.594930843207494</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>32.79</t>
+          <t>0.263838284050561</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>0.365730520426024</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>0.190703822891348</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>55.88</t>
+          <t>0.475414608482178</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>0.477037250199488</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>0.188976364149489</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>0.539128769921039</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>75.05</t>
+          <t>0.695161291846628</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>69.61</t>
+          <t>0.648794737092306</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>86.77</t>
+          <t>0.818867840674003</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>30.58</t>
+          <t>0.31141819474453</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>69.75</t>
+          <t>0.699328355746902</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>0.4106053656789</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>0.294352896689323</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2741,144 +2746,144 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-55.98</t>
+          <t>-0.558738371086529</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-39</t>
+          <t>-0.428923587888718</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-24.22</t>
+          <t>-0.27062509069465</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-18.74</t>
+          <t>-0.23189926467039</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-44.55</t>
+          <t>-0.479751202056791</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-22.06</t>
+          <t>-0.270762226173169</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-22.6</t>
+          <t>-0.274890885690337</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-16.15</t>
+          <t>-0.21704704390499</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-16.36</t>
+          <t>-0.212604771062125</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-20.15</t>
+          <t>-0.2515516129475</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-0.256506048718356</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-14.89</t>
+          <t>-0.20206773081512</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-0.0871862202490501</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-0.106784830937801</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>0.0363490729903821</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>-15.23</t>
+          <t>-0.185109279159848</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.0358073789987817</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>-18.5</t>
+          <t>-0.209746606979208</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>-16.85</t>
+          <t>-0.20319071067045</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-0.131947679861372</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>-0.0516129034582418</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>-20.55</t>
+          <t>-0.181289216925108</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>-21.59</t>
+          <t>-0.160473788222039</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>-33.75</t>
+          <t>-0.296033855408905</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-29.17</t>
+          <t>-0.247725229828415</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-42.06</t>
+          <t>-0.369060481056491</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>-37.51</t>
+          <t>-0.332036185282975</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2888,144 +2893,144 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>51.83</t>
+          <t>0.276408083930474</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t>0.00356515151932557</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>0.1051411889632</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>0.0244230432853727</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>-0.071924238457169</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.152574101849482</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>-0.0960318225934457</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.184179440177033</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.147764006850421</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-0.243557713150453</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>-9.03</t>
+          <t>-0.218696700816553</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>-9.9</t>
+          <t>-0.232627470372444</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>-0.0880793280385641</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>-0.116991080589742</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>-0.0737719735260904</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>-0.104005145731891</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>-0.0424999029059656</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>-0.00429167784335904</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>0.0269554816304056</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>0.0946354781411511</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>0.132244776738823</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>0.354981081283401</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>0.346338408044219</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>0.193720490476523</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>44.57</t>
+          <t>0.233332922308418</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>0.21032891603678</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>0.148155745852299</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3035,144 +3040,144 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>69.74</t>
+          <t>0.463338922130909</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-96.55</t>
+          <t>-0.969589910680607</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>-93.98</t>
+          <t>-0.946294775165212</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-89.97</t>
+          <t>-0.909722684516741</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-79.85</t>
+          <t>-0.819557944464155</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.35</t>
+          <t>-0.787291353544778</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-70.08</t>
+          <t>-0.729572629034647</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-62.93</t>
+          <t>-0.663661954786911</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-61.97</t>
+          <t>-0.644829577179954</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-63.2</t>
+          <t>-0.662790172879293</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>-50.61</t>
+          <t>-0.527309916509678</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>-48.91</t>
+          <t>-0.511868528660374</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>0.457484036496269</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>47.04</t>
+          <t>0.411666834270787</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>57.93</t>
+          <t>0.546308682199673</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>-32.23</t>
+          <t>-0.382468011666542</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>101.76</t>
+          <t>0.880294224886</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>-32.5</t>
+          <t>-0.379899069417749</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>-45.41</t>
+          <t>-0.486829313429754</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>113.89</t>
+          <t>1.0284981741022</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>107.99</t>
+          <t>0.989308394310535</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>113.75</t>
+          <t>1.03917674333918</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>108.35</t>
+          <t>1.01879494392921</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>104.88</t>
+          <t>1.0111134124913</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>108.54</t>
+          <t>1.05980390105779</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>124.16</t>
+          <t>1.23998645301249</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>104.67</t>
+          <t>1.01263187909229</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3182,144 +3187,144 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>166.91</t>
+          <t>1.4618867877512</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>198.7</t>
+          <t>1.51318062300534</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>225.25</t>
+          <t>1.87932187910981</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>212.28</t>
+          <t>1.72425728736456</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>210.06</t>
+          <t>1.6875930987534</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>227.55</t>
+          <t>1.88322799545234</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>192.06</t>
+          <t>1.51184360567589</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>231.17</t>
+          <t>1.93920625414703</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>183.52</t>
+          <t>1.49362153522001</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>177.92</t>
+          <t>1.42520099844398</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>191.73</t>
+          <t>1.52937520634215</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>216.25</t>
+          <t>1.78771510749317</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>227.18</t>
+          <t>1.94576411781356</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>193.36</t>
+          <t>1.59165282204584</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>1.84638001155864</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>264.5</t>
+          <t>2.29767662567827</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>230.96</t>
+          <t>2.02226444745116</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>266.31</t>
+          <t>2.37938417657712</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>283.31</t>
+          <t>2.47571635261168</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>254.14</t>
+          <t>2.28164746169196</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>256.75</t>
+          <t>2.25639147748874</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>254.29</t>
+          <t>2.29212058076555</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>234.67</t>
+          <t>2.16336603372786</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>240.52</t>
+          <t>2.1331380988143</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>237.2</t>
+          <t>2.22989104112755</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>199.32</t>
+          <t>1.93052183371712</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>230.29</t>
+          <t>2.10999086947735</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3329,144 +3334,144 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-77.12</t>
+          <t>-0.771477740749012</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-275.6</t>
+          <t>-2.76019266124764</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>-283.38</t>
+          <t>-2.8380449383656</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-268.46</t>
+          <t>-2.6867117254102</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-259.66</t>
+          <t>-2.59828282460887</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-265.26</t>
+          <t>-2.6550799870099</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-265.51</t>
+          <t>-2.65899335471864</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-267.27</t>
+          <t>-2.67544700470701</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>-271.24</t>
+          <t>-2.71778663936113</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-252.26</t>
+          <t>-2.52579598621803</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>-255.79</t>
+          <t>-2.56047771194004</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>-262.19</t>
+          <t>-2.62440459183032</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>-257.42</t>
+          <t>-2.57780298337323</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>-265.64</t>
+          <t>-2.65792533847798</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>-261.18</t>
+          <t>-2.61249502171871</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>-272.74</t>
+          <t>-2.72593506482478</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>-274.5</t>
+          <t>-2.74058043868402</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>-287.32</t>
+          <t>-2.86694422383346</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>-298.76</t>
+          <t>-2.9802019293653</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>-82.33</t>
+          <t>-0.824396277156617</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-80.63</t>
+          <t>-0.807338766822576</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>-78.45</t>
+          <t>-0.785471314155885</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>-77.62</t>
+          <t>-0.777178249389625</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>-76.26</t>
+          <t>-0.763739832145878</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-75.37</t>
+          <t>-0.754373280181339</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>-76.9</t>
+          <t>-0.769752188735132</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>-77.45</t>
+          <t>-0.775124510673394</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3476,144 +3481,144 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>108.58</t>
+          <t>0.943121013735968</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-184.04</t>
+          <t>-1.78062170354416</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-198.64</t>
+          <t>-1.91605163282007</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-235.95</t>
+          <t>-2.23931585780956</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-229.47</t>
+          <t>-2.20297761106103</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-204.83</t>
+          <t>-1.98089862602888</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-233.58</t>
+          <t>-2.24494653766339</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-237.66</t>
+          <t>-2.27261051165013</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-255.71</t>
+          <t>-2.40896900218817</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-221.7</t>
+          <t>-2.13613092258017</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-220.08</t>
+          <t>-2.10316377933929</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-218.11</t>
+          <t>-2.07287838771751</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-215.08</t>
+          <t>-2.05714784333409</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-228.16</t>
+          <t>-2.18681874964773</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-218.12</t>
+          <t>-2.0645048575988</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>-203.83</t>
+          <t>-1.94665734831098</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>-202.49</t>
+          <t>-1.93289329473079</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>-195.56</t>
+          <t>-1.87288877938738</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>-180.41</t>
+          <t>-1.74447507213545</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>152.86</t>
+          <t>1.30236078252673</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>122.18</t>
+          <t>1.05456388285958</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>92.88</t>
+          <t>0.794454857202776</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>100.96</t>
+          <t>0.879432825168461</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>84.29</t>
+          <t>0.717062423610419</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>82.82</t>
+          <t>0.70927070103545</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>79.47</t>
+          <t>0.671476611533426</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>83.55</t>
+          <t>0.705849482896229</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3623,144 +3628,144 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>232.75</t>
+          <t>1.97911699327633</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-34.01</t>
+          <t>-0.408775701442012</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-19.01</t>
+          <t>-0.25088473846189</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-21.86</t>
+          <t>-0.27286831656878</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-32.14</t>
+          <t>-0.368248778469255</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-26.81</t>
+          <t>-0.313990505171403</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-24.81</t>
+          <t>-0.303539676319841</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>-0.00399251611322737</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.0633643580225822</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-12.01</t>
+          <t>-0.163010835452051</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-18.73</t>
+          <t>-0.239946091166034</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-0.115209331443216</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>51.77</t>
+          <t>0.435251831671204</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>62.14</t>
+          <t>0.518258380601629</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>0.00318273296568083</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-0.0166937759624766</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-0.0792083561968689</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>13.47</t>
+          <t>0.0623229941595684</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>-16.35</t>
+          <t>-0.224032976242554</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>33.61</t>
+          <t>0.278909522950799</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>0.0145225677688301</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.0302040834196182</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>38.63</t>
+          <t>0.37662279869272</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>0.392629124757075</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>0.324091023528419</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>19.36</t>
+          <t>0.200013764410381</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>0.249050962343898</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3770,144 +3775,144 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>0.0812965052547474</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-43.53</t>
+          <t>-0.508823382383978</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-35.83</t>
+          <t>-0.443442775878555</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-31.66</t>
+          <t>-0.406844147363063</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-42.2</t>
+          <t>-0.50187311392108</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-41.31</t>
+          <t>-0.48650038724113</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-36.02</t>
+          <t>-0.444500337001758</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-34.74</t>
+          <t>-0.427928515531484</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-39.94</t>
+          <t>-0.466918691171692</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-36.39</t>
+          <t>-0.441560195588257</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-37.14</t>
+          <t>-0.44546799008742</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-32.23</t>
+          <t>-0.407115407401149</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>32.78</t>
+          <t>0.175086579332006</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>0.176797777248663</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-18.69</t>
+          <t>-0.285654394908025</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>-21.71</t>
+          <t>-0.314867704390882</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>-18.15</t>
+          <t>-0.284213327160273</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>-12.96</t>
+          <t>-0.245210067554328</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-0.248214315774786</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>52.05</t>
+          <t>0.34211947176898</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>63.52</t>
+          <t>0.444165880536186</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>0.438121792635272</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>67.68</t>
+          <t>0.49295556126346</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>59.42</t>
+          <t>0.407580996389107</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>76.53</t>
+          <t>0.562906272658126</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>61.05</t>
+          <t>0.42195860454846</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>67.19</t>
+          <t>0.470255956627585</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3917,144 +3922,144 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-31.39</t>
+          <t>-0.401105083594002</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-0.071262327209996</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>0.0895348677736836</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>18.47</t>
+          <t>0.0964160546494801</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>0.0280425719701614</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-0.143049888492703</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.106826083410186</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>0.0639819306334899</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>0.165986347423819</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>20.86</t>
+          <t>0.107070805904968</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>23.99</t>
+          <t>0.142215521037615</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>0.215860456540095</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>67.24</t>
+          <t>0.60966751663272</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>61.74</t>
+          <t>0.487165584406286</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>84.01</t>
+          <t>0.681804723672926</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>0.453547353032384</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>0.523852829039483</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>57.12</t>
+          <t>0.406064578020567</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>73.25</t>
+          <t>0.56888322136635</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>59.07</t>
+          <t>0.429696481810532</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>77.26</t>
+          <t>0.579355646597483</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>89.25</t>
+          <t>0.714588068564982</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>115.31</t>
+          <t>0.9405839599814</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>76.18</t>
+          <t>0.585768774767929</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>79.46</t>
+          <t>0.620738908882011</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>80.53</t>
+          <t>0.620130927151476</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>52.36</t>
+          <t>0.337910675548578</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4064,144 +4069,144 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>60.64</t>
+          <t>0.451942497506151</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-40.23</t>
+          <t>-0.453394052397765</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-40.64</t>
+          <t>-0.449367748826139</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-21.64</t>
+          <t>-0.28541793915062</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-39.6</t>
+          <t>-0.453891940662304</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-40.45</t>
+          <t>-0.457595545771201</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-0.392704849405332</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-33.3</t>
+          <t>-0.389831556309615</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-32.33</t>
+          <t>-0.365952987965394</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-33.07</t>
+          <t>-0.385007045539498</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>-27.79</t>
+          <t>-0.337228068506893</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>-35.36</t>
+          <t>-0.403524250839091</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>-14.44</t>
+          <t>-0.184502569318384</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-11.53</t>
+          <t>-0.184514649530017</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-0.0951894690498749</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>8.99</t>
+          <t>-0.0034057373298243</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>0.0290972276267116</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>-0.066525313895038</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>-0.0607566407446695</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>80.06</t>
+          <t>0.632164157332281</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>170.44</t>
+          <t>1.48896701795086</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>145.83</t>
+          <t>1.24562747411909</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>129.09</t>
+          <t>1.12137602599159</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>178.08</t>
+          <t>1.55068724301167</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>153.11</t>
+          <t>1.34279994868492</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>157.55</t>
+          <t>1.36830155796635</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>160.56</t>
+          <t>1.38047842065593</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4211,144 +4216,144 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>214.52</t>
+          <t>1.50653132324956</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>154.4</t>
+          <t>1.23574651574939</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>64.38</t>
+          <t>0.380074414682406</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>85.52</t>
+          <t>0.593170669115453</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>77.26</t>
+          <t>0.508945871028073</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>68.82</t>
+          <t>0.417295188254956</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>92.53</t>
+          <t>0.620218836489374</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>51.88</t>
+          <t>0.298917642102896</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>84.69</t>
+          <t>0.585306702382459</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>0.487736629296665</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>78.72</t>
+          <t>0.536705250361087</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>90.23</t>
+          <t>0.631099994720988</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>137.56</t>
+          <t>1.06588182781419</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>138.14</t>
+          <t>1.03460138298607</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>124.29</t>
+          <t>0.966997306847734</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>128.82</t>
+          <t>0.96867152673986</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>104.6</t>
+          <t>0.768079415737277</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>104.57</t>
+          <t>0.756135366561729</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>133.17</t>
+          <t>1.02374796672467</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>144.05</t>
+          <t>1.135618743676</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>151.42</t>
+          <t>1.18678248350974</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>146.07</t>
+          <t>1.13940577613962</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>143.52</t>
+          <t>1.11479527279509</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>100.53</t>
+          <t>0.729917206386575</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>145.24</t>
+          <t>1.11794054624874</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>132.66</t>
+          <t>1.00111573615306</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>214.62</t>
+          <t>1.73903763108696</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4358,144 +4363,144 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>146.15</t>
+          <t>1.19634995744402</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-42.9</t>
+          <t>-0.506563387776996</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>-54.42</t>
+          <t>-0.606359171627978</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-67.5</t>
+          <t>-0.719560742182638</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-69.4</t>
+          <t>-0.737594526119367</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.55</t>
+          <t>-0.799546656305882</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-83.21</t>
+          <t>-0.856956697808272</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-78.68</t>
+          <t>-0.817216024157751</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-69.98</t>
+          <t>-0.744044748953061</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-74.84</t>
+          <t>-0.782959942185625</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>-80.22</t>
+          <t>-0.828052231102369</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>-81.99</t>
+          <t>-0.844089738683645</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>-77.57</t>
+          <t>-0.803816141227113</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>-82.09</t>
+          <t>-0.84439799662783</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>-81.55</t>
+          <t>-0.841020982536083</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>-83.09</t>
+          <t>-0.853775229648638</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>-78.21</t>
+          <t>-0.814237558257263</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>-84.5</t>
+          <t>-0.867121019779954</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>-84.65</t>
+          <t>-0.869473536737949</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>-84.79</t>
+          <t>-0.869450242041637</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-81.48</t>
+          <t>-0.84265417232166</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>-81.32</t>
+          <t>-0.839472909542111</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>-81.7</t>
+          <t>-0.841840382746588</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>-86.05</t>
+          <t>-0.879576640469833</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>-83.09</t>
+          <t>-0.854048996784067</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>-84.12</t>
+          <t>-0.863171282804759</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>-83.99</t>
+          <t>-0.862704754707247</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4505,144 +4510,144 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>1.46641780993356</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>92.95</t>
+          <t>0.825337922738863</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>94.63</t>
+          <t>0.786961016256854</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>105.28</t>
+          <t>0.855039762797099</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>0.602911348349194</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>0.472894614082426</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>77.92</t>
+          <t>0.55393676490768</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>0.467031895908561</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>158.31</t>
+          <t>1.29773582553755</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>247.34</t>
+          <t>2.09690187335733</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>192.56</t>
+          <t>1.60627135215291</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>0.876598978596727</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>119.51</t>
+          <t>0.978183910296335</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>129.66</t>
+          <t>1.03991866943706</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>202.52</t>
+          <t>1.68587818352957</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>191.76</t>
+          <t>1.58349162452879</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>136.86</t>
+          <t>1.02782347432652</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>144.22</t>
+          <t>1.08710059687817</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>1.17147429358015</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>245.01</t>
+          <t>2.00828711139206</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>186.01</t>
+          <t>1.48051204446283</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>300.66</t>
+          <t>2.52040522955878</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>205.8</t>
+          <t>1.63879861800028</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>198.25</t>
+          <t>1.61357207340535</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>222.23</t>
+          <t>1.81846464121432</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>216.26</t>
+          <t>1.72709145323414</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>305.29</t>
+          <t>2.6060041204167</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4652,144 +4657,144 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>306.02</t>
+          <t>2.98237173789849</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-33.81</t>
+          <t>-0.344465903815501</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>-14.68</t>
+          <t>-0.155462565555947</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-29.04</t>
+          <t>-0.29708049280087</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-0.0368731405276166</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>0.111018585129776</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>0.368061357214527</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>0.29558010401661</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>40.09</t>
+          <t>0.37298274683175</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>0.437332224029022</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>50.55</t>
+          <t>0.464573530491242</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>63.96</t>
+          <t>0.595735009413236</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>92.15</t>
+          <t>0.879342151536122</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>93.32</t>
+          <t>0.877096549219535</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>127.68</t>
+          <t>1.22235704842003</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>260.41</t>
+          <t>2.5085962935747</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>365.08</t>
+          <t>3.52718420400042</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>168.79</t>
+          <t>1.61602264483492</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>188.64</t>
+          <t>1.82380542820213</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>550.68</t>
+          <t>5.40238836684991</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>547.7</t>
+          <t>5.32766694094312</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>671.28</t>
+          <t>6.50971186747004</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>594.2</t>
+          <t>5.82518017301614</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>715.82</t>
+          <t>7.04217952035378</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>657.1</t>
+          <t>6.42760139745292</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>688.18</t>
+          <t>6.72851629661521</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>859.22</t>
+          <t>8.35964336356013</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4799,144 +4804,144 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>280.22</t>
+          <t>2.38370334177301</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-0.205161958812137</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>64.25</t>
+          <t>0.416771896642983</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>45.84</t>
+          <t>0.263944728113028</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>-0.0321712609940293</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>0.161712924179181</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>0.0185501438277609</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>-0.0631691249750607</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>-13.34</t>
+          <t>-0.247433367700948</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>0.096402056018529</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-0.0341339161024432</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-0.131530847086436</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>0.116298981358706</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>-0.0322052980285117</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>-30.52</t>
+          <t>-0.409968249146472</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>-9.75</t>
+          <t>-0.232046968617418</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>21.04</t>
+          <t>0.0273984615294895</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>0.0823497625666567</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>0.186046336492681</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>82.83</t>
+          <t>0.540340773009421</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>124.88</t>
+          <t>0.894464552991451</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>0.291553705874327</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>37.41</t>
+          <t>0.160887997502561</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>73.56</t>
+          <t>0.48688432533475</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>172.66</t>
+          <t>1.34346397875273</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>198.95</t>
+          <t>1.55647529112846</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>126.59</t>
+          <t>0.924247123310797</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4946,144 +4951,144 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>-0.111958452990471</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-48.58</t>
+          <t>-0.552336375249227</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-34.56</t>
+          <t>-0.429202496752046</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-39.59</t>
+          <t>-0.473588858245044</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-41.79</t>
+          <t>-0.4968187915876</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-44.54</t>
+          <t>-0.52053670118634</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-43.95</t>
+          <t>-0.514444056102492</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-46.39</t>
+          <t>-0.533011027024259</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-47.93</t>
+          <t>-0.542025181490755</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-42.99</t>
+          <t>-0.501988320713915</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-42.54</t>
+          <t>-0.4977620142185</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-42.79</t>
+          <t>-0.505829326763565</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-0.356689066003568</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-35.67</t>
+          <t>-0.447162236928524</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-47.75</t>
+          <t>-0.54520116081995</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>-48.08</t>
+          <t>-0.552739817440288</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>-37.26</t>
+          <t>-0.46523575460313</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>-47.06</t>
+          <t>-0.547247308628396</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>-46.26</t>
+          <t>-0.540234545092167</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>-38.89</t>
+          <t>-0.472489710968026</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>-41.88</t>
+          <t>-0.49773979073256</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>-43.02</t>
+          <t>-0.50531398838315</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>-46.58</t>
+          <t>-0.535797487105395</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>-47.68</t>
+          <t>-0.546155141055574</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>-48.64</t>
+          <t>-0.553173629254867</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>-55.8</t>
+          <t>-0.616410109342729</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>-57.05</t>
+          <t>-0.627503505077249</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5093,144 +5098,144 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>237.52</t>
+          <t>2.16207287789972</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>-0.0475554556719461</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>0.150390937093623</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>35.72</t>
+          <t>0.246291442187862</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>0.302493239111498</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>0.279025455552394</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>0.337864765506803</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>58.18</t>
+          <t>0.418310945625218</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>64.37</t>
+          <t>0.488332840400084</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>95.77</t>
+          <t>0.75532601106548</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>79.37</t>
+          <t>0.619920799585941</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>95.85</t>
+          <t>0.759268732926081</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>106.85</t>
+          <t>0.870764055130985</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>78.29</t>
+          <t>0.598584185907262</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>112.31</t>
+          <t>0.912830063002306</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>109.07</t>
+          <t>0.874459503881881</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>115.66</t>
+          <t>0.904839122371626</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>105.17</t>
+          <t>0.813015437969875</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>103.13</t>
+          <t>0.796920482797522</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>197.95</t>
+          <t>1.64621578781053</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>198.66</t>
+          <t>1.62059221912492</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>240.18</t>
+          <t>2.02134324882572</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>156.04</t>
+          <t>1.27705507560648</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>184.7</t>
+          <t>1.51295574320281</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>198.16</t>
+          <t>1.65017364390897</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>201.59</t>
+          <t>1.61532394867401</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>170.21</t>
+          <t>1.38058530194625</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5240,144 +5245,144 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>63.87</t>
+          <t>0.297866404138737</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-0.165641952505183</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>-0.0833968403843224</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>-0.0944445242725201</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-0.154737497724342</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.143200442198436</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>-0.130392809526125</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>-0.0949782474522823</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-0.0527676961718887</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>-0.101347150594487</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>-0.0275626456009153</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>-0.0638073138503426</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>19.39</t>
+          <t>0.0295993909548464</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>-0.0439100130091528</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>18.57</t>
+          <t>0.0154074528448223</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>0.0779359349271171</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>0.122570502936441</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>43.49</t>
+          <t>0.221448319163879</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>0.111658804570911</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>113.22</t>
+          <t>0.806099027722944</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>127.53</t>
+          <t>0.94704121515675</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>118.55</t>
+          <t>0.865712222703001</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>0.78129979746689</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>118.08</t>
+          <t>0.879169371021364</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>129.66</t>
+          <t>0.947736067617623</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>117.8</t>
+          <t>0.82839859280188</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>131.54</t>
+          <t>0.966819771855156</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5387,144 +5392,144 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>352.73</t>
+          <t>3.46314932633971</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>12.93</t>
+          <t>0.108264803802019</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>-13.94</t>
+          <t>-0.16009493412126</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-9.16</t>
+          <t>-0.11354769129973</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-8.5</t>
+          <t>-0.109163777007543</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-34.16</t>
+          <t>-0.362831417722494</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-43.8</t>
+          <t>-0.4579415196977</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-55.29</t>
+          <t>-0.567370639046447</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>-14.84</t>
+          <t>-0.18993886006093</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-12.17</t>
+          <t>-0.156767110474281</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>0.232632459799355</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>0.148717644167247</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>0.284732044175337</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>0.214425927324787</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>63.88</t>
+          <t>0.536770234704125</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>61.49</t>
+          <t>0.51372447200436</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>0.348487653451445</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>0.324402116713282</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>68.83</t>
+          <t>0.58325605762373</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>223.07</t>
+          <t>2.00319192144493</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>283.03</t>
+          <t>2.51742017598456</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>356.61</t>
+          <t>3.20267658267904</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>271.41</t>
+          <t>2.43799501696369</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>309.11</t>
+          <t>2.72832097564416</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>358.13</t>
+          <t>3.16694461973609</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>261.02</t>
+          <t>2.28349889570746</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>308.39</t>
+          <t>2.78716294842687</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5534,144 +5539,144 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>0.703441478416062</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>223.36</t>
+          <t>2.32108384294554</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>121.22</t>
+          <t>1.0926084786635</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>157.52</t>
+          <t>1.42496376227923</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>172.64</t>
+          <t>1.56498871633282</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>87.35</t>
+          <t>0.793994143783566</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>105.75</t>
+          <t>0.967233560646593</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>143.99</t>
+          <t>1.36425991536276</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>147.34</t>
+          <t>1.41396356534507</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>163.2</t>
+          <t>1.5103264341788</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>114.22</t>
+          <t>1.05715626581399</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>124.9</t>
+          <t>1.19177416264832</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>140.44</t>
+          <t>1.3681107413288</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>153.84</t>
+          <t>1.48934217946711</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>170.78</t>
+          <t>1.63082202338238</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>107.31</t>
+          <t>0.987954429772111</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>107.73</t>
+          <t>0.95761913093137</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>64.77</t>
+          <t>0.560488775105722</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>88.84</t>
+          <t>0.791097494226754</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>104.85</t>
+          <t>0.953918087712722</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>128.58</t>
+          <t>1.18894119971227</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>131.12</t>
+          <t>1.22832037260462</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>80.52</t>
+          <t>0.731580759339142</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>0.827143746798229</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>86.88</t>
+          <t>0.786174538973234</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>82.62</t>
+          <t>0.742179156104377</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>123.7</t>
+          <t>1.15623442079333</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5681,144 +5686,144 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>172.83</t>
+          <t>1.4329437504159</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>396.5</t>
+          <t>3.39896673737281</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>200.28</t>
+          <t>1.62422837440353</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>332.39</t>
+          <t>2.89171365603776</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>346.65</t>
+          <t>3.03272195178968</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>293.87</t>
+          <t>2.57921828842562</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>299.59</t>
+          <t>2.58172977013556</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>271.5</t>
+          <t>2.25476804086086</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>245.89</t>
+          <t>2.05303652876524</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>284.74</t>
+          <t>2.30975043203027</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>271.12</t>
+          <t>2.15388144804454</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>272.91</t>
+          <t>2.12524787043508</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>206.81</t>
+          <t>1.61164689564933</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>268.65</t>
+          <t>2.11962027154996</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>243.07</t>
+          <t>1.92301341266288</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>179.59</t>
+          <t>1.36005297036061</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>176.09</t>
+          <t>1.30265862672449</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>177.05</t>
+          <t>1.26518200002016</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>193.04</t>
+          <t>1.40999965486951</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>158.17</t>
+          <t>1.15582106569285</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>223.77</t>
+          <t>1.6777832284631</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>236.04</t>
+          <t>1.77437572452326</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>193.83</t>
+          <t>1.41005753535284</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>200.59</t>
+          <t>1.42451073910044</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>184.21</t>
+          <t>1.30437286145636</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>147.8</t>
+          <t>0.993615503268341</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>206.55</t>
+          <t>1.48054419699883</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5828,144 +5833,144 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>58.23</t>
+          <t>0.328180671873104</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>0.0187695140348094</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>43.81</t>
+          <t>0.241671857354976</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>0.030152344473209</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>13.61</t>
+          <t>-0.0424514922536927</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-0.0767246801152397</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>-0.0428947673184669</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>0.0653905968819799</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>23.83</t>
+          <t>0.0458375040587218</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>0.000620653490045253</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>22.11</t>
+          <t>0.0131704687487015</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>0.0153918294040363</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>30.63</t>
+          <t>0.132884849051712</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>29.42</t>
+          <t>0.133965819311076</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>-8.3</t>
+          <t>-0.223899656701287</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>-19.48</t>
+          <t>-0.326455239751045</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>-16.28</t>
+          <t>-0.305334061676207</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>-22.26</t>
+          <t>-0.370363745504386</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>-14.45</t>
+          <t>-0.290751117095773</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>42.98</t>
+          <t>0.172587121083392</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>17.54</t>
+          <t>-0.0239335299671108</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>36.53</t>
+          <t>0.136467038106787</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>0.0267538963684335</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>-0.0750530539436948</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>0.0219814390152915</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-0.217397051794384</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>-0.00136590379785306</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5975,144 +5980,144 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-50.22</t>
+          <t>-0.62156423958519</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>-0.0219720787586395</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>0.0453946330176209</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>0.0678532826139386</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>-0.0324812327422411</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>-0.0310631994805558</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>-0.0925256913648537</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>-0.107796936382906</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>-0.00231460719669285</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>0.00923918486748798</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>22.11</t>
+          <t>-0.0147988192647006</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>31.19</t>
+          <t>0.0374918544041927</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>44.09</t>
+          <t>0.16169020029979</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>0.0412254245605588</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>42.54</t>
+          <t>0.158389523669085</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>51.96</t>
+          <t>0.230827633836974</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>36.71</t>
+          <t>0.0912950593194803</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>0.0651979362770452</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>40.37</t>
+          <t>0.109854853963881</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>59.72</t>
+          <t>0.264254815118943</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>49.29</t>
+          <t>0.181590271116963</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>58.42</t>
+          <t>0.232330801452771</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>65.89</t>
+          <t>0.292809820159505</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>0.0532723000341213</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>0.0710304053764934</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>0.0661098786493333</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>-0.0384316545913638</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6122,144 +6127,144 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>517.36</t>
+          <t>4.45504385430462</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-147.39</t>
+          <t>-1.42152841827244</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>-130.22</t>
+          <t>-1.27390168867821</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-109.92</t>
+          <t>-1.08985017507999</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-109.47</t>
+          <t>-1.0858484571841</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-115.5</t>
+          <t>-1.13753358283479</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-75.55</t>
+          <t>-0.785259372171257</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-109.92</t>
+          <t>-1.08665914711442</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>-85.93</t>
+          <t>-0.877505796082311</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-70.88</t>
+          <t>-0.750382687862434</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>-72.08</t>
+          <t>-0.758377263967008</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>-44.04</t>
+          <t>-0.509007371166229</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>-13.54</t>
+          <t>-0.265648092085226</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>0.127587143887505</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>29.86</t>
+          <t>0.15109117925963</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>-10.12</t>
+          <t>-0.195580496750504</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>0.330978250205526</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>50.51</t>
+          <t>0.289704399379171</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>28.43</t>
+          <t>0.133679811364445</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>347.9</t>
+          <t>2.97230153443856</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>205.12</t>
+          <t>1.68680223854508</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>181.68</t>
+          <t>1.49057848241764</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>190.8</t>
+          <t>1.55937951457216</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>204.66</t>
+          <t>1.65953789397732</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>231.66</t>
+          <t>1.98315630848769</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>352.85</t>
+          <t>3.16220100856965</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>235.01</t>
+          <t>2.07565766578098</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6269,144 +6274,144 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>-0.00265174182861216</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-46.62</t>
+          <t>-0.514082511220574</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>-54.43</t>
+          <t>-0.583166506128234</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-58.1</t>
+          <t>-0.61444157746179</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-52.23</t>
+          <t>-0.564454147803086</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-67.63</t>
+          <t>-0.700664100054662</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-59.27</t>
+          <t>-0.628456748605236</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-62.58</t>
+          <t>-0.661319983736118</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>-60.75</t>
+          <t>-0.642790406656013</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-65.23</t>
+          <t>-0.69002549228454</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>-58.16</t>
+          <t>-0.624025049247287</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>-57.91</t>
+          <t>-0.621902194837065</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>-45.84</t>
+          <t>-0.507356506651186</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>-43.31</t>
+          <t>-0.493463297364886</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>-18.54</t>
+          <t>-0.271470932329526</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>-34.13</t>
+          <t>-0.407501329219562</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>-30.2</t>
+          <t>-0.375782139453425</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>-37.44</t>
+          <t>-0.433751075077636</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>-30.9</t>
+          <t>-0.381995221954012</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>0.105960353430077</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>0.285249009154088</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>0.155487753117259</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>0.367700173353489</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>85.22</t>
+          <t>0.5932783113904</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>0.470312814957914</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>76.11</t>
+          <t>0.539247780090064</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>93.53</t>
+          <t>0.64944306144609</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6416,144 +6421,144 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>-26.84</t>
+          <t>-0.271412193612938</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>63.59</t>
+          <t>0.526012294241761</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>0.525658082694429</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>53.12</t>
+          <t>0.40752844358392</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>0.359835774783442</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>39.61</t>
+          <t>0.284490757394641</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>0.206282566268583</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>27.09</t>
+          <t>0.162736270100767</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>0.26297234349905</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>0.156183724718034</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>0.146471867856838</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>31.74</t>
+          <t>0.20331633755007</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>0.367591617736375</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>45.11</t>
+          <t>0.348363812504731</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>0.355276109169797</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>0.380349713676636</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>56.25</t>
+          <t>0.444993895200877</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>51.49</t>
+          <t>0.372601381959042</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>0.430235954824275</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>83.87</t>
+          <t>0.707988844247295</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>72.66</t>
+          <t>0.597207205095886</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>0.68547932381124</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>84.88</t>
+          <t>0.739710175921988</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>63.51</t>
+          <t>0.517108050179794</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>74.66</t>
+          <t>0.636332629527371</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>79.35</t>
+          <t>0.663322009292703</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>66.23</t>
+          <t>0.537693694128357</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6565,7 +6570,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6575,144 +6580,144 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>0.270809436796882</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-112.94</t>
+          <t>-1.1239066345221</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>-112.46</t>
+          <t>-1.12050405923172</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-110.87</t>
+          <t>-1.10535447997368</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-112.82</t>
+          <t>-1.12287468171552</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-112.84</t>
+          <t>-1.12310940756109</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-113.81</t>
+          <t>-1.1324437296949</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-113.67</t>
+          <t>-1.13168566504705</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>-112.22</t>
+          <t>-1.11822863151893</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-112.37</t>
+          <t>-1.11892781249414</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>-109.7</t>
+          <t>-1.09337771812301</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-109.32</t>
+          <t>-1.09010478745804</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>-104.43</t>
+          <t>-1.04310267476552</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>-99.44</t>
+          <t>-0.994629153861289</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>-100.42</t>
+          <t>-1.00402681657355</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>-96.56</t>
+          <t>-0.966751624796704</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>-90.77</t>
+          <t>-0.91079191671667</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>-97.02</t>
+          <t>-0.971364549199299</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>-95.08</t>
+          <t>-0.95251715176329</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>0.3537249400049</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>0.398767313227183</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>32.78</t>
+          <t>0.292305033834779</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>37.36</t>
+          <t>0.331124563689267</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>29.28</t>
+          <t>0.26008435491021</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>0.374777294400602</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>29.28</t>
+          <t>0.263227326014448</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>28.09</t>
+          <t>0.249158556913149</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6722,144 +6727,144 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>138.89</t>
+          <t>0.949349837128722</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-0.273344114892844</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-0.328331783704827</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-21.31</t>
+          <t>-0.372399924918943</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-0.285630878608316</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-18.22</t>
+          <t>-0.336714923541021</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-0.139702583697664</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>22.72</t>
+          <t>0.0922024704658098</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>26.52</t>
+          <t>0.134157673453583</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>0.0100584809342814</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>-0.060031124165728</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>-0.0370439841617629</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>68.17</t>
+          <t>0.473623088615564</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>0.47895242542276</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>50.04</t>
+          <t>0.291881333664567</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>13.47</t>
+          <t>-0.0142104417122264</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>0.289203978112716</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>0.193487042445581</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>0.222208529784016</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>0.498981680287753</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>86.52</t>
+          <t>0.715766269526858</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>79.81</t>
+          <t>0.679911673488712</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>0.701580861541585</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>80.42</t>
+          <t>0.577438948275506</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>72.79</t>
+          <t>0.62395807345223</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>60.61</t>
+          <t>0.508207412489205</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>123.76</t>
+          <t>1.04252599068093</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6869,144 +6874,144 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-0.125946893604415</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>-0.0556547231940007</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>-8.56</t>
+          <t>-0.169980148145213</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-0.149955241855313</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>-0.0248674270073402</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-12.04</t>
+          <t>-0.200815493627875</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-14.79</t>
+          <t>-0.228340284006227</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.129620584009673</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>-0.102968909635677</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.136262545290183</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>-12.95</t>
+          <t>-0.239938219423274</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.158320907058326</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>0.00150343154314969</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>-0.0186215763022449</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-0.150950968433156</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-0.143763825050552</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-0.169982039810294</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>-17.7</t>
+          <t>-0.260664818414224</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>-27.66</t>
+          <t>-0.353103885279886</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>0.180138975569439</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>23.82</t>
+          <t>0.110373746066645</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>0.0628918012199413</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>22.17</t>
+          <t>0.118386010281642</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>37.38</t>
+          <t>0.243755532807918</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>0.140091871168241</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>49.78</t>
+          <t>0.365100615299589</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>14.37</t>
+          <t>0.00443589854374005</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7016,144 +7021,144 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>-13.42</t>
+          <t>-0.182643861811621</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>-0.0557151382679737</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-0.102832668356579</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-0.112258091503229</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>0.159913238617353</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>-0.0261426416467558</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>-0.0535883652610487</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>-0.0290368505281084</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>0.102708521406252</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-6.8</t>
+          <t>-0.134254490937296</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-0.0818160105902797</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.0653251582192966</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>-14.02</t>
+          <t>-0.205205288684157</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>-18.97</t>
+          <t>-0.252795331906827</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-0.114610103609605</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.0906243371768689</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-0.120733455036115</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>-13.19</t>
+          <t>-0.203510879105031</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>-22.84</t>
+          <t>-0.292703462001963</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-0.170939375570493</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>12.95</t>
+          <t>0.0440090131127138</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>-0.179219129465781</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-0.108796765193049</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>-0.127969194870229</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-0.165726779984467</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>-29.33</t>
+          <t>-0.343418546375755</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>-18.2</t>
+          <t>-0.241810228930002</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7163,144 +7168,144 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>111.48</t>
+          <t>0.972720410405786</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>0.414075388454964</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>0.405369603713727</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>59.56</t>
+          <t>0.48296317049474</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>0.355464651780949</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>0.328051731588985</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>48.81</t>
+          <t>0.377564272418161</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>50.57</t>
+          <t>0.389927883472975</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>0.1590754386366</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>0.0884175510690937</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>0.0946890091713666</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>-0.0226183473234848</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>0.261065009555723</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>0.268886979583716</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>0.226967789661881</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>0.127508992292655</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>0.0129532307255393</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>0.132623320098089</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>0.111590355377275</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>161.32</t>
+          <t>1.45742453442634</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>145.77</t>
+          <t>1.30721074595426</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>268.03</t>
+          <t>2.46158929796744</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>134.87</t>
+          <t>1.24215329560972</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>0.988994363993556</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>146.61</t>
+          <t>1.3756462787234</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>141.89</t>
+          <t>1.32266804726879</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>173.86</t>
+          <t>1.59426148269715</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7310,144 +7315,144 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>113.39</t>
+          <t>1.07784378974365</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-142.18</t>
+          <t>-1.4120281803311</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>-148.59</t>
+          <t>-1.47864104035731</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-143.89</t>
+          <t>-1.42676346821399</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-142.9</t>
+          <t>-1.41181461662437</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-143.64</t>
+          <t>-1.41866107040986</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-151.89</t>
+          <t>-1.49587486391973</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-148.33</t>
+          <t>-1.46371767868151</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>-139.05</t>
+          <t>-1.37214982665296</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-142.71</t>
+          <t>-1.41359353689349</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>-140.5</t>
+          <t>-1.39312354641219</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>-133.25</t>
+          <t>-1.32009225596455</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>-122.88</t>
+          <t>-1.21770617643931</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>-118.92</t>
+          <t>-1.1811077252324</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>-113.8</t>
+          <t>-1.13162518974842</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>-120.61</t>
+          <t>-1.19773243991212</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-1.08300904626031</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>-122.74</t>
+          <t>-1.21873072006609</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>-135.12</t>
+          <t>-1.3418546886576</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>59.86</t>
+          <t>0.53700689989347</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>81.35</t>
+          <t>0.731023381362847</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>0.737558117402425</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>68.22</t>
+          <t>0.622610341424178</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>85.55</t>
+          <t>0.790227692432811</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>74.83</t>
+          <t>0.701093694889782</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>83.01</t>
+          <t>0.776925051930084</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>97.16</t>
+          <t>0.901444547313041</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7457,144 +7462,144 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>172.44</t>
+          <t>1.51568790484149</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>0.0395227997148133</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>-0.0515804736176878</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.0772762362765004</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-0.131289362749934</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>-0.0278962386692413</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-0.108127465043297</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.10584993725979</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>0.0313418692378606</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>-0.00596546929779407</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>0.0163040020365506</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>0.0672844728370374</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>18.47</t>
+          <t>0.114307944360826</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>26.94</t>
+          <t>0.176753700421669</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>0.0816036314447803</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>75.26</t>
+          <t>0.634614722489363</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>137.27</t>
+          <t>1.2168906567366</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>35.81</t>
+          <t>0.261432331257993</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>0.179031244119071</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>163.93</t>
+          <t>1.46518376007225</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>161.75</t>
+          <t>1.46074024954318</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>172.12</t>
+          <t>1.54848119543075</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>167.33</t>
+          <t>1.52596708362612</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>165.81</t>
+          <t>1.48926741290025</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>165.4</t>
+          <t>1.49305018552409</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>178.87</t>
+          <t>1.61000508314406</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>189.36</t>
+          <t>1.72287658516529</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7604,144 +7609,144 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>248.78</t>
+          <t>1.90376692676583</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>0.0808065235510995</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>0.181280306457841</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.317667382411684</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>43.09</t>
+          <t>0.248075401346144</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>76.49</t>
+          <t>0.571473892842623</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>62.49</t>
+          <t>0.448540793221015</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>74.63</t>
+          <t>0.55732246610366</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>105.19</t>
+          <t>0.822620184995855</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>0.767112795549296</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>128.51</t>
+          <t>1.03065114549567</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>114.83</t>
+          <t>0.918821019519661</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>0.683498177431864</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>116.04</t>
+          <t>0.915065719741213</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>191.22</t>
+          <t>1.59597799690141</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>165.27</t>
+          <t>1.36942877608704</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>167.55</t>
+          <t>1.37730838286667</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>172.27</t>
+          <t>1.4464051880266</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>177.75</t>
+          <t>1.49420560780373</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>293.01</t>
+          <t>2.5369839522863</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>272.3</t>
+          <t>2.36113996845084</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>279.69</t>
+          <t>2.41597034408014</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>258.81</t>
+          <t>2.2530949029299</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>313.38</t>
+          <t>2.75001536274791</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>320.12</t>
+          <t>2.81010692376116</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>308.87</t>
+          <t>2.70692917395135</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>263.6</t>
+          <t>2.28664955757081</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7751,144 +7756,144 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>133.97</t>
+          <t>1.20261890396238</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>101.56</t>
+          <t>0.841604120738112</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>101.86</t>
+          <t>0.845020339545043</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>83.61</t>
+          <t>0.674739642092929</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>92.99</t>
+          <t>0.753077963826776</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>76.48</t>
+          <t>0.601628048513207</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>74.41</t>
+          <t>0.582033493093511</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>0.577160034387465</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>71.93</t>
+          <t>0.570659630054374</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>66.99</t>
+          <t>0.522217848325629</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>63.98</t>
+          <t>0.499777806002122</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>68.51</t>
+          <t>0.541319872928903</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>0.917394207769028</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>0.634683632849375</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>77.76</t>
+          <t>0.629027063446183</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>0.783402386294417</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>0.550739291230207</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>102.75</t>
+          <t>0.846478245458578</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>106.32</t>
+          <t>0.891426817053643</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>122.78</t>
+          <t>1.09091717051595</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>121.49</t>
+          <t>1.08055481252163</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>116.44</t>
+          <t>1.03212227294907</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>147.96</t>
+          <t>1.33192297016933</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>124.06</t>
+          <t>1.11179379119806</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>124.75</t>
+          <t>1.11329896690809</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>127.06</t>
+          <t>1.13341000856226</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>119.43</t>
+          <t>1.06069479363515</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7898,137 +7903,137 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>38.13</t>
+          <t>0.346313329492119</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>0.0877978641240849</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-0.115705500390572</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-11.64</t>
+          <t>-0.155113483866076</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-17.39</t>
+          <t>-0.233931912802006</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-31.13</t>
+          <t>-0.362106441027692</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-39.87</t>
+          <t>-0.442042969486496</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-44.48</t>
+          <t>-0.485724516383136</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>-40.86</t>
+          <t>-0.441202003445677</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-47.43</t>
+          <t>-0.506715437525402</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>-48.53</t>
+          <t>-0.509761694088889</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>-53.69</t>
+          <t>-0.562658891599863</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>-45.44</t>
+          <t>-0.477819251371504</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>-49.04</t>
+          <t>-0.518618018557861</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>-45.07</t>
+          <t>-0.476198976021612</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>-41.22</t>
+          <t>-0.44326927909384</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>-36.52</t>
+          <t>-0.399288106397256</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>-36.32</t>
+          <t>-0.401379588450823</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>-38.23</t>
+          <t>-0.409916083428638</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>0.0106653371232268</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>0.00729231488432447</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.0339742633770209</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-0.0954654491527126</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-0.152919802309313</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-0.0852413606836741</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>-13.5</t>
+          <t>-0.172656638613427</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-0.143307712325408</t>
         </is>
       </c>
     </row>
@@ -8070,6 +8075,11 @@
           <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8104,6 +8114,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
